--- a/data/results/hypothesis_tests_output.xlsx
+++ b/data/results/hypothesis_tests_output.xlsx
@@ -449,7 +449,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>-2.414</v>
+        <v>-1.419</v>
       </c>
     </row>
     <row r="3">
@@ -459,7 +459,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>8.544</v>
+        <v>2.003</v>
       </c>
     </row>
     <row r="4">
@@ -469,7 +469,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>38.2</v>
+        <v>38.7</v>
       </c>
     </row>
     <row r="5">
@@ -479,7 +479,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>61.3</v>
+        <v>60.8</v>
       </c>
     </row>
     <row r="6">
@@ -499,7 +499,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>-0.9688</v>
+        <v>-0.7444</v>
       </c>
     </row>
     <row r="8">
@@ -509,7 +509,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.0509</v>
+        <v>0.0429</v>
       </c>
     </row>
   </sheetData>
@@ -580,25 +580,25 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>7725</v>
+        <v>7624</v>
       </c>
       <c r="C2" t="n">
-        <v>-0.0969</v>
+        <v>-0.08799999999999999</v>
       </c>
       <c r="D2" t="n">
         <v>-0.05</v>
       </c>
       <c r="E2" t="n">
-        <v>0.1331</v>
+        <v>0.1084</v>
       </c>
       <c r="F2" t="n">
-        <v>6991</v>
+        <v>8463</v>
       </c>
       <c r="G2" t="n">
         <v>0</v>
       </c>
       <c r="H2" t="n">
-        <v>-0.999</v>
+        <v>-0.998</v>
       </c>
       <c r="I2" t="b">
         <v>1</v>
@@ -611,22 +611,22 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>2438</v>
+        <v>2409</v>
       </c>
       <c r="C3" t="n">
-        <v>-0.07829999999999999</v>
+        <v>-0.0689</v>
       </c>
       <c r="D3" t="n">
         <v>0</v>
       </c>
       <c r="E3" t="n">
-        <v>0.1412</v>
+        <v>0.1125</v>
       </c>
       <c r="F3" t="n">
-        <v>347.5</v>
+        <v>221</v>
       </c>
       <c r="G3" t="n">
-        <v>7.424801780492135e-184</v>
+        <v>6.093107736187674e-179</v>
       </c>
       <c r="H3" t="n">
         <v>-0.999</v>
@@ -642,25 +642,25 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>2370</v>
+        <v>2348</v>
       </c>
       <c r="C4" t="n">
-        <v>-0.1061</v>
+        <v>-0.1007</v>
       </c>
       <c r="D4" t="n">
-        <v>-0.082</v>
+        <v>-0.0805</v>
       </c>
       <c r="E4" t="n">
-        <v>0.1159</v>
+        <v>0.1023</v>
       </c>
       <c r="F4" t="n">
-        <v>883.5</v>
+        <v>1678.5</v>
       </c>
       <c r="G4" t="n">
-        <v>3.284107582411501e-283</v>
+        <v>1.153913583083691e-279</v>
       </c>
       <c r="H4" t="n">
-        <v>-0.999</v>
+        <v>-0.998</v>
       </c>
       <c r="I4" t="b">
         <v>1</v>
@@ -673,22 +673,22 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1453</v>
+        <v>1429</v>
       </c>
       <c r="C5" t="n">
-        <v>-0.1172</v>
+        <v>-0.1071</v>
       </c>
       <c r="D5" t="n">
-        <v>-0.0955</v>
+        <v>-0.092</v>
       </c>
       <c r="E5" t="n">
-        <v>0.1248</v>
+        <v>0.098</v>
       </c>
       <c r="F5" t="n">
-        <v>173</v>
+        <v>315</v>
       </c>
       <c r="G5" t="n">
-        <v>1.444746123064182e-183</v>
+        <v>2.695475378308521e-180</v>
       </c>
       <c r="H5" t="n">
         <v>-0.999</v>
@@ -704,25 +704,25 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1464</v>
+        <v>1438</v>
       </c>
       <c r="C6" t="n">
-        <v>-0.0927</v>
+        <v>-0.0801</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.025</v>
+        <v>-0.0194</v>
       </c>
       <c r="E6" t="n">
-        <v>0.1481</v>
+        <v>0.1147</v>
       </c>
       <c r="F6" t="n">
-        <v>421</v>
+        <v>224</v>
       </c>
       <c r="G6" t="n">
-        <v>3.758645213905247e-135</v>
+        <v>3.134751261434113e-130</v>
       </c>
       <c r="H6" t="n">
-        <v>-0.997</v>
+        <v>-0.999</v>
       </c>
       <c r="I6" t="b">
         <v>1</v>
@@ -771,10 +771,10 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>2438</v>
+        <v>2409</v>
       </c>
       <c r="C2" t="n">
-        <v>0.6004</v>
+        <v>0.6076</v>
       </c>
       <c r="D2" t="n">
         <v>0.6</v>
@@ -787,10 +787,10 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>2370</v>
+        <v>2348</v>
       </c>
       <c r="C3" t="n">
-        <v>0.2396</v>
+        <v>0.2419</v>
       </c>
       <c r="D3" t="n">
         <v>0.1</v>
@@ -803,10 +803,10 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1453</v>
+        <v>1429</v>
       </c>
       <c r="C4" t="n">
-        <v>0.184</v>
+        <v>0.1871</v>
       </c>
       <c r="D4" t="n">
         <v>0.1111</v>
@@ -819,10 +819,10 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1464</v>
+        <v>1438</v>
       </c>
       <c r="C5" t="n">
-        <v>0.2343</v>
+        <v>0.2386</v>
       </c>
       <c r="D5" t="n">
         <v>0.125</v>
@@ -835,7 +835,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>7725</v>
+        <v>7624</v>
       </c>
       <c r="C6" t="inlineStr"/>
       <c r="D6" t="inlineStr"/>
@@ -847,7 +847,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>2928.142</v>
+        <v>3035.114</v>
       </c>
       <c r="C7" t="inlineStr"/>
       <c r="D7" t="inlineStr"/>
@@ -871,7 +871,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.3791</v>
+        <v>0.3982</v>
       </c>
       <c r="C9" t="inlineStr"/>
       <c r="D9" t="inlineStr"/>
@@ -957,13 +957,13 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>2438</v>
+        <v>2409</v>
       </c>
       <c r="E2" t="n">
-        <v>2370</v>
+        <v>2348</v>
       </c>
       <c r="F2" t="n">
-        <v>4925981</v>
+        <v>4872664</v>
       </c>
       <c r="G2" t="n">
         <v>0</v>
@@ -972,7 +972,7 @@
         <v>0</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.705</v>
+        <v>-0.723</v>
       </c>
       <c r="J2" t="inlineStr">
         <is>
@@ -998,13 +998,13 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>2438</v>
+        <v>2409</v>
       </c>
       <c r="E3" t="n">
-        <v>1453</v>
+        <v>1429</v>
       </c>
       <c r="F3" t="n">
-        <v>3224158</v>
+        <v>3165994</v>
       </c>
       <c r="G3" t="n">
         <v>0</v>
@@ -1013,7 +1013,7 @@
         <v>0</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.82</v>
+        <v>-0.839</v>
       </c>
       <c r="J3" t="inlineStr">
         <is>
@@ -1039,13 +1039,13 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>2438</v>
+        <v>2409</v>
       </c>
       <c r="E4" t="n">
-        <v>1464</v>
+        <v>1438</v>
       </c>
       <c r="F4" t="n">
-        <v>3106321</v>
+        <v>3043310</v>
       </c>
       <c r="G4" t="n">
         <v>0</v>
@@ -1054,7 +1054,7 @@
         <v>0</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.741</v>
+        <v>-0.757</v>
       </c>
       <c r="J4" t="inlineStr">
         <is>
@@ -1080,22 +1080,22 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>2370</v>
+        <v>2348</v>
       </c>
       <c r="E5" t="n">
-        <v>1453</v>
+        <v>1429</v>
       </c>
       <c r="F5" t="n">
-        <v>1791076.5</v>
+        <v>1734460.5</v>
       </c>
       <c r="G5" t="n">
-        <v>0.02518984458192365</v>
+        <v>0.06061469461774677</v>
       </c>
       <c r="H5" t="n">
-        <v>0.02518984458192365</v>
+        <v>0.06061469461774677</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.04</v>
+        <v>-0.034</v>
       </c>
       <c r="J5" t="inlineStr">
         <is>
@@ -1103,7 +1103,7 @@
         </is>
       </c>
       <c r="K5" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6">
@@ -1121,22 +1121,22 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>2370</v>
+        <v>2348</v>
       </c>
       <c r="E6" t="n">
-        <v>1464</v>
+        <v>1438</v>
       </c>
       <c r="F6" t="n">
-        <v>1613808</v>
+        <v>1552474</v>
       </c>
       <c r="G6" t="n">
-        <v>0.000119482993402634</v>
+        <v>1.025698074760277e-05</v>
       </c>
       <c r="H6" t="n">
-        <v>0.0002389659868052679</v>
+        <v>2.051396149520554e-05</v>
       </c>
       <c r="I6" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="J6" t="inlineStr">
         <is>
@@ -1162,22 +1162,22 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>1453</v>
+        <v>1429</v>
       </c>
       <c r="E7" t="n">
-        <v>1464</v>
+        <v>1438</v>
       </c>
       <c r="F7" t="n">
-        <v>919507.5</v>
+        <v>882041.5</v>
       </c>
       <c r="G7" t="n">
-        <v>3.142129754751801e-11</v>
+        <v>5.397877790619521e-12</v>
       </c>
       <c r="H7" t="n">
-        <v>9.426389264255405e-11</v>
+        <v>1.619363337185856e-11</v>
       </c>
       <c r="I7" t="n">
-        <v>0.135</v>
+        <v>0.142</v>
       </c>
       <c r="J7" t="inlineStr">
         <is>
@@ -1402,10 +1402,10 @@
         <v>62</v>
       </c>
       <c r="C2" t="n">
-        <v>2438</v>
+        <v>2409</v>
       </c>
       <c r="D2" t="n">
-        <v>2.5</v>
+        <v>2.6</v>
       </c>
     </row>
     <row r="3">
@@ -1418,10 +1418,10 @@
         <v>530</v>
       </c>
       <c r="C3" t="n">
-        <v>2370</v>
+        <v>2348</v>
       </c>
       <c r="D3" t="n">
-        <v>22.4</v>
+        <v>22.6</v>
       </c>
     </row>
     <row r="4">
@@ -1434,10 +1434,10 @@
         <v>472</v>
       </c>
       <c r="C4" t="n">
-        <v>1453</v>
+        <v>1429</v>
       </c>
       <c r="D4" t="n">
-        <v>32.5</v>
+        <v>33</v>
       </c>
     </row>
     <row r="5">
@@ -1450,10 +1450,10 @@
         <v>312</v>
       </c>
       <c r="C5" t="n">
-        <v>1464</v>
+        <v>1438</v>
       </c>
       <c r="D5" t="n">
-        <v>21.3</v>
+        <v>21.7</v>
       </c>
     </row>
     <row r="6">
@@ -1466,10 +1466,10 @@
         <v>1376</v>
       </c>
       <c r="C6" t="n">
-        <v>7725</v>
+        <v>7624</v>
       </c>
       <c r="D6" t="n">
-        <v>17.8</v>
+        <v>18</v>
       </c>
     </row>
   </sheetData>
@@ -1530,16 +1530,16 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>38704</v>
+        <v>38070</v>
       </c>
       <c r="C2" t="n">
-        <v>-0.0058</v>
+        <v>-0.0066</v>
       </c>
       <c r="D2" t="n">
-        <v>0.0058</v>
+        <v>0.0066</v>
       </c>
       <c r="E2" t="n">
-        <v>0.2528970236684138</v>
+        <v>0.1986945399768647</v>
       </c>
       <c r="F2" t="b">
         <v>1</v>
@@ -1557,16 +1557,16 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>38704</v>
+        <v>38070</v>
       </c>
       <c r="C3" t="n">
-        <v>-0.0004</v>
+        <v>0.0008</v>
       </c>
       <c r="D3" t="n">
-        <v>0.0004</v>
+        <v>0.0008</v>
       </c>
       <c r="E3" t="n">
-        <v>0.9387827498223394</v>
+        <v>0.8815268496915168</v>
       </c>
       <c r="F3" t="b">
         <v>1</v>
@@ -1584,16 +1584,16 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>38704</v>
+        <v>38070</v>
       </c>
       <c r="C4" t="n">
-        <v>-0.0077</v>
+        <v>-0.007900000000000001</v>
       </c>
       <c r="D4" t="n">
-        <v>0.0077</v>
+        <v>0.007900000000000001</v>
       </c>
       <c r="E4" t="n">
-        <v>0.1319478788756214</v>
+        <v>0.1248350965590836</v>
       </c>
       <c r="F4" t="b">
         <v>1</v>
@@ -1607,16 +1607,16 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>38704</v>
+        <v>38070</v>
       </c>
       <c r="C5" t="n">
-        <v>0.0169</v>
+        <v>0.0179</v>
       </c>
       <c r="D5" t="n">
-        <v>0.0169</v>
+        <v>0.0179</v>
       </c>
       <c r="E5" t="n">
-        <v>0.0008962779983507639</v>
+        <v>0.0004627493243134449</v>
       </c>
       <c r="F5" t="b">
         <v>1</v>
@@ -1630,16 +1630,16 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>38704</v>
+        <v>38070</v>
       </c>
       <c r="C6" t="n">
-        <v>0.0036</v>
+        <v>0.0037</v>
       </c>
       <c r="D6" t="n">
-        <v>0.0036</v>
+        <v>0.0037</v>
       </c>
       <c r="E6" t="n">
-        <v>0.4771149390712763</v>
+        <v>0.4697382142910732</v>
       </c>
       <c r="F6" t="b">
         <v>1</v>
@@ -1653,7 +1653,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>38704</v>
+        <v>38070</v>
       </c>
       <c r="C7" t="inlineStr"/>
       <c r="D7" t="inlineStr"/>
@@ -1705,7 +1705,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>38704</v>
+        <v>38070</v>
       </c>
     </row>
     <row r="4">
@@ -1715,7 +1715,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.653</v>
+        <v>0.666</v>
       </c>
     </row>
     <row r="5">
@@ -1725,7 +1725,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.681</v>
+        <v>0.694</v>
       </c>
     </row>
     <row r="6">
@@ -1735,7 +1735,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>23.894</v>
+        <v>22.331</v>
       </c>
     </row>
     <row r="7">
@@ -1745,7 +1745,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.2002606517714081</v>
+        <v>0.2680790548488654</v>
       </c>
     </row>
     <row r="8">
